--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -5,9 +5,9 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Test Case" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Failed Case" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Execution log" state="visible" r:id="rId7"/>
+    <sheet sheetId="2" name="Test Cases" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Failed Tests" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Execution Logs" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Performance Metrics" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -15,69 +15,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="164">
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Test Suite Name</t>
-  </si>
-  <si>
-    <t>Appium E2E Automation Suite</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="235">
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/15/2026, 4:43:17 PM</t>
-  </si>
-  <si>
-    <t>Environment</t>
+    <t>Device Name</t>
+  </si>
+  <si>
+    <t>Android Version</t>
+  </si>
+  <si>
+    <t>Total Tests</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Pass Percentage</t>
+  </si>
+  <si>
+    <t>Execution Duration</t>
+  </si>
+  <si>
+    <t>6/15/2026, 4:53:59 PM</t>
   </si>
   <si>
     <t>Android Emulator (Pixel 6)</t>
   </si>
   <si>
-    <t>Total Test Cases</t>
-  </si>
-  <si>
-    <t>Passed Cases</t>
-  </si>
-  <si>
-    <t>Failed Cases</t>
-  </si>
-  <si>
-    <t>Success Rate</t>
+    <t>13.0</t>
   </si>
   <si>
     <t>96.67%</t>
   </si>
   <si>
+    <t>00:06:12</t>
+  </si>
+  <si>
     <t>Test ID</t>
   </si>
   <si>
-    <t>Scenario Description</t>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Device</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Execution Time</t>
+    <t>Start Time</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>Duration</t>
   </si>
   <si>
     <t>TC_APP_001</t>
   </si>
   <si>
+    <t>Mobile Onboarding</t>
+  </si>
+  <si>
     <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
   </si>
   <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>4.13s</t>
+    <t>4:47:59 PM</t>
+  </si>
+  <si>
+    <t>4:48:05 PM</t>
+  </si>
+  <si>
+    <t>3.31s</t>
   </si>
   <si>
     <t>TC_APP_002</t>
@@ -86,7 +107,13 @@
     <t>TC_APP_002 - Verify splash screen transition duration</t>
   </si>
   <si>
-    <t>2.31s</t>
+    <t>4:48:11 PM</t>
+  </si>
+  <si>
+    <t>4:48:17 PM</t>
+  </si>
+  <si>
+    <t>2.69s</t>
   </si>
   <si>
     <t>TC_APP_003</t>
@@ -95,7 +122,13 @@
     <t>TC_APP_003 - Verify registration page display inside app</t>
   </si>
   <si>
-    <t>3.81s</t>
+    <t>4:48:23 PM</t>
+  </si>
+  <si>
+    <t>4:48:29 PM</t>
+  </si>
+  <si>
+    <t>3.43s</t>
   </si>
   <si>
     <t>TC_APP_004</t>
@@ -104,7 +137,13 @@
     <t>TC_APP_004 - Verify new account registration via mobile form</t>
   </si>
   <si>
-    <t>2.96s</t>
+    <t>4:48:35 PM</t>
+  </si>
+  <si>
+    <t>4:48:41 PM</t>
+  </si>
+  <si>
+    <t>4.36s</t>
   </si>
   <si>
     <t>TC_APP_005</t>
@@ -113,7 +152,13 @@
     <t>TC_APP_005 - Verify app displays validation errors on registration</t>
   </si>
   <si>
-    <t>3.05s</t>
+    <t>4:48:47 PM</t>
+  </si>
+  <si>
+    <t>4:48:53 PM</t>
+  </si>
+  <si>
+    <t>4.02s</t>
   </si>
   <si>
     <t>TC_APP_006</t>
@@ -122,7 +167,13 @@
     <t>TC_APP_006 - Verify Login screen load and fields check</t>
   </si>
   <si>
-    <t>4.06s</t>
+    <t>4:48:59 PM</t>
+  </si>
+  <si>
+    <t>4:49:05 PM</t>
+  </si>
+  <si>
+    <t>2.56s</t>
   </si>
   <si>
     <t>TC_APP_007</t>
@@ -131,7 +182,13 @@
     <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
   </si>
   <si>
-    <t>3.54s</t>
+    <t>4:49:11 PM</t>
+  </si>
+  <si>
+    <t>4:49:17 PM</t>
+  </si>
+  <si>
+    <t>3.58s</t>
   </si>
   <si>
     <t>TC_APP_008</t>
@@ -140,16 +197,31 @@
     <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
   </si>
   <si>
-    <t>4.36s</t>
+    <t>4:49:23 PM</t>
+  </si>
+  <si>
+    <t>4:49:29 PM</t>
+  </si>
+  <si>
+    <t>4.81s</t>
   </si>
   <si>
     <t>TC_APP_009</t>
   </si>
   <si>
+    <t>Transactions Activity</t>
+  </si>
+  <si>
     <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
   </si>
   <si>
-    <t>4.58s</t>
+    <t>4:49:35 PM</t>
+  </si>
+  <si>
+    <t>4:49:41 PM</t>
+  </si>
+  <si>
+    <t>3.39s</t>
   </si>
   <si>
     <t>TC_APP_010</t>
@@ -158,7 +230,13 @@
     <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
   </si>
   <si>
-    <t>4.10s</t>
+    <t>4:49:47 PM</t>
+  </si>
+  <si>
+    <t>4:49:53 PM</t>
+  </si>
+  <si>
+    <t>2.13s</t>
   </si>
   <si>
     <t>TC_APP_011</t>
@@ -167,13 +245,28 @@
     <t>TC_APP_011 - Verify add income input dialog form</t>
   </si>
   <si>
+    <t>4:49:59 PM</t>
+  </si>
+  <si>
+    <t>4:50:05 PM</t>
+  </si>
+  <si>
+    <t>4.49s</t>
+  </si>
+  <si>
     <t>TC_APP_012</t>
   </si>
   <si>
     <t>TC_APP_012 - Verify add income form submission and balance update</t>
   </si>
   <si>
-    <t>2.10s</t>
+    <t>4:50:11 PM</t>
+  </si>
+  <si>
+    <t>4:50:17 PM</t>
+  </si>
+  <si>
+    <t>2.32s</t>
   </si>
   <si>
     <t>TC_APP_013</t>
@@ -182,7 +275,13 @@
     <t>TC_APP_013 - Verify add expense input dialog form</t>
   </si>
   <si>
-    <t>2.11s</t>
+    <t>4:50:23 PM</t>
+  </si>
+  <si>
+    <t>4:50:29 PM</t>
+  </si>
+  <si>
+    <t>4.99s</t>
   </si>
   <si>
     <t>TC_APP_014</t>
@@ -191,7 +290,13 @@
     <t>TC_APP_014 - Verify add expense form submission and balance update</t>
   </si>
   <si>
-    <t>4.09s</t>
+    <t>4:50:35 PM</t>
+  </si>
+  <si>
+    <t>4:50:41 PM</t>
+  </si>
+  <si>
+    <t>3.83s</t>
   </si>
   <si>
     <t>TC_APP_015</t>
@@ -200,13 +305,28 @@
     <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
   </si>
   <si>
+    <t>4:50:47 PM</t>
+  </si>
+  <si>
+    <t>4:50:53 PM</t>
+  </si>
+  <si>
+    <t>2.53s</t>
+  </si>
+  <si>
     <t>TC_APP_016</t>
   </si>
   <si>
     <t>TC_APP_016 - Verify transaction title update and save action</t>
   </si>
   <si>
-    <t>3.70s</t>
+    <t>4:50:59 PM</t>
+  </si>
+  <si>
+    <t>4:51:05 PM</t>
+  </si>
+  <si>
+    <t>3.80s</t>
   </si>
   <si>
     <t>TC_APP_017</t>
@@ -215,7 +335,13 @@
     <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
   </si>
   <si>
-    <t>4.46s</t>
+    <t>4:51:11 PM</t>
+  </si>
+  <si>
+    <t>4:51:17 PM</t>
+  </si>
+  <si>
+    <t>2.88s</t>
   </si>
   <si>
     <t>TC_APP_018</t>
@@ -224,16 +350,31 @@
     <t>TC_APP_018 - Verify search transaction input box filters list</t>
   </si>
   <si>
-    <t>4.52s</t>
+    <t>4:51:23 PM</t>
+  </si>
+  <si>
+    <t>4:51:29 PM</t>
+  </si>
+  <si>
+    <t>4.53s</t>
   </si>
   <si>
     <t>TC_APP_019</t>
   </si>
   <si>
+    <t>Alerts OS</t>
+  </si>
+  <si>
     <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
   </si>
   <si>
-    <t>3.30s</t>
+    <t>4:51:35 PM</t>
+  </si>
+  <si>
+    <t>4:51:41 PM</t>
+  </si>
+  <si>
+    <t>4.97s</t>
   </si>
   <si>
     <t>TC_APP_020</t>
@@ -242,7 +383,13 @@
     <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
   </si>
   <si>
-    <t>2.16s</t>
+    <t>4:51:47 PM</t>
+  </si>
+  <si>
+    <t>4:51:53 PM</t>
+  </si>
+  <si>
+    <t>3.89s</t>
   </si>
   <si>
     <t>TC_APP_021</t>
@@ -251,16 +398,31 @@
     <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
   </si>
   <si>
-    <t>2.17s</t>
+    <t>4:51:59 PM</t>
+  </si>
+  <si>
+    <t>4:52:05 PM</t>
+  </si>
+  <si>
+    <t>3.74s</t>
   </si>
   <si>
     <t>TC_APP_022</t>
   </si>
   <si>
+    <t>User Profiles</t>
+  </si>
+  <si>
     <t>TC_APP_022 - Verify profile update form saves new username</t>
   </si>
   <si>
-    <t>3.44s</t>
+    <t>4:52:11 PM</t>
+  </si>
+  <si>
+    <t>4:52:17 PM</t>
+  </si>
+  <si>
+    <t>4.70s</t>
   </si>
   <si>
     <t>TC_APP_023</t>
@@ -269,7 +431,13 @@
     <t>TC_APP_023 - Verify profile image upload simulation</t>
   </si>
   <si>
-    <t>3.47s</t>
+    <t>4:52:23 PM</t>
+  </si>
+  <si>
+    <t>4:52:29 PM</t>
+  </si>
+  <si>
+    <t>2.74s</t>
   </si>
   <si>
     <t>TC_APP_024</t>
@@ -278,7 +446,13 @@
     <t>TC_APP_024 - Verify change password form validation checks</t>
   </si>
   <si>
-    <t>2.51s</t>
+    <t>4:52:35 PM</t>
+  </si>
+  <si>
+    <t>4:52:41 PM</t>
+  </si>
+  <si>
+    <t>3.00s</t>
   </si>
   <si>
     <t>TC_APP_025</t>
@@ -287,7 +461,13 @@
     <t>TC_APP_025 - Verify successful change password submission</t>
   </si>
   <si>
-    <t>2.77s</t>
+    <t>4:52:47 PM</t>
+  </si>
+  <si>
+    <t>4:52:53 PM</t>
+  </si>
+  <si>
+    <t>3.08s</t>
   </si>
   <si>
     <t>TC_APP_026</t>
@@ -296,7 +476,13 @@
     <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
   </si>
   <si>
-    <t>4.48s</t>
+    <t>4:52:59 PM</t>
+  </si>
+  <si>
+    <t>4:53:05 PM</t>
+  </si>
+  <si>
+    <t>3.94s</t>
   </si>
   <si>
     <t>TC_APP_027</t>
@@ -305,7 +491,13 @@
     <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
   </si>
   <si>
-    <t>2.72s</t>
+    <t>4:53:11 PM</t>
+  </si>
+  <si>
+    <t>4:53:17 PM</t>
+  </si>
+  <si>
+    <t>2.07s</t>
   </si>
   <si>
     <t>TC_APP_028</t>
@@ -314,7 +506,13 @@
     <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
   </si>
   <si>
-    <t>3.59s</t>
+    <t>4:53:23 PM</t>
+  </si>
+  <si>
+    <t>4:53:29 PM</t>
+  </si>
+  <si>
+    <t>4.79s</t>
   </si>
   <si>
     <t>TC_APP_029</t>
@@ -323,7 +521,13 @@
     <t>TC_APP_029 - Verify logout button click asks confirmation</t>
   </si>
   <si>
-    <t>4.94s</t>
+    <t>4:53:35 PM</t>
+  </si>
+  <si>
+    <t>4:53:41 PM</t>
+  </si>
+  <si>
+    <t>3.38s</t>
   </si>
   <si>
     <t>TC_APP_030</t>
@@ -332,22 +536,25 @@
     <t>TC_APP_030 - Verify successful logout clears local cache database</t>
   </si>
   <si>
-    <t>Failed</t>
+    <t>4:53:47 PM</t>
+  </si>
+  <si>
+    <t>4:53:53 PM</t>
   </si>
   <si>
     <t>12.40s</t>
   </si>
   <si>
-    <t>Test ID / Name</t>
-  </si>
-  <si>
-    <t>Failure Message</t>
-  </si>
-  <si>
-    <t>Screenshot Reference</t>
-  </si>
-  <si>
-    <t>Target Activity / Component</t>
+    <t>Test Name</t>
+  </si>
+  <si>
+    <t>Failure Reason</t>
+  </si>
+  <si>
+    <t>Screenshot Path</t>
+  </si>
+  <si>
+    <t>Activity Name</t>
   </si>
   <si>
     <t>AssertionError: expected UserSession.isCached() to be false</t>
@@ -362,13 +569,16 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>Step / Action Description</t>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Result</t>
   </si>
   <si>
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T11:13:17.654Z</t>
+    <t>2026-06-15T11:23:59.335Z</t>
   </si>
   <si>
     <t>Execution of TC_APP_001</t>
@@ -473,10 +683,13 @@
     <t>Database cache not cleared completely after logout</t>
   </si>
   <si>
-    <t>Performance Metric</t>
+    <t>Metric Name</t>
   </si>
   <si>
     <t>Target Component</t>
+  </si>
+  <si>
+    <t>Value / Duration</t>
   </si>
   <si>
     <t>App Launch Time</t>
@@ -571,16 +784,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -588,12 +801,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -933,75 +1160,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="E2" s="2">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="F2" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1012,447 +1238,822 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="65" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="65" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="C18" s="3" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>19</v>
+        <v>162</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>105</v>
+        <v>131</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>106</v>
+        <v>10</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -1463,41 +2064,55 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>113</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -1508,447 +2123,541 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C21" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C22" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="C23" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="C24" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>144</v>
+        <v>213</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>145</v>
+        <v>214</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>146</v>
+        <v>215</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>147</v>
+        <v>216</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>148</v>
+        <v>217</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>151</v>
+        <v>218</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -1964,76 +2673,76 @@
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>152</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>153</v>
+        <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>157</v>
+      <c r="A2" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>157</v>
+      <c r="A3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>157</v>
+      <c r="A4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="234">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 4:53:59 PM</t>
+    <t>6/15/2026, 5:27:13 PM</t>
   </si>
   <si>
     <t>Android Emulator (Pixel 6)</t>
@@ -92,13 +92,13 @@
     <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
   </si>
   <si>
-    <t>4:47:59 PM</t>
-  </si>
-  <si>
-    <t>4:48:05 PM</t>
-  </si>
-  <si>
-    <t>3.31s</t>
+    <t>5:21:13 PM</t>
+  </si>
+  <si>
+    <t>5:21:19 PM</t>
+  </si>
+  <si>
+    <t>2.13s</t>
   </si>
   <si>
     <t>TC_APP_002</t>
@@ -107,13 +107,13 @@
     <t>TC_APP_002 - Verify splash screen transition duration</t>
   </si>
   <si>
-    <t>4:48:11 PM</t>
-  </si>
-  <si>
-    <t>4:48:17 PM</t>
-  </si>
-  <si>
-    <t>2.69s</t>
+    <t>5:21:25 PM</t>
+  </si>
+  <si>
+    <t>5:21:31 PM</t>
+  </si>
+  <si>
+    <t>2.28s</t>
   </si>
   <si>
     <t>TC_APP_003</t>
@@ -122,13 +122,13 @@
     <t>TC_APP_003 - Verify registration page display inside app</t>
   </si>
   <si>
-    <t>4:48:23 PM</t>
-  </si>
-  <si>
-    <t>4:48:29 PM</t>
-  </si>
-  <si>
-    <t>3.43s</t>
+    <t>5:21:37 PM</t>
+  </si>
+  <si>
+    <t>5:21:43 PM</t>
+  </si>
+  <si>
+    <t>3.32s</t>
   </si>
   <si>
     <t>TC_APP_004</t>
@@ -137,13 +137,13 @@
     <t>TC_APP_004 - Verify new account registration via mobile form</t>
   </si>
   <si>
-    <t>4:48:35 PM</t>
-  </si>
-  <si>
-    <t>4:48:41 PM</t>
-  </si>
-  <si>
-    <t>4.36s</t>
+    <t>5:21:49 PM</t>
+  </si>
+  <si>
+    <t>5:21:55 PM</t>
+  </si>
+  <si>
+    <t>4.92s</t>
   </si>
   <si>
     <t>TC_APP_005</t>
@@ -152,13 +152,13 @@
     <t>TC_APP_005 - Verify app displays validation errors on registration</t>
   </si>
   <si>
-    <t>4:48:47 PM</t>
-  </si>
-  <si>
-    <t>4:48:53 PM</t>
-  </si>
-  <si>
-    <t>4.02s</t>
+    <t>5:22:01 PM</t>
+  </si>
+  <si>
+    <t>5:22:07 PM</t>
+  </si>
+  <si>
+    <t>3.57s</t>
   </si>
   <si>
     <t>TC_APP_006</t>
@@ -167,13 +167,13 @@
     <t>TC_APP_006 - Verify Login screen load and fields check</t>
   </si>
   <si>
-    <t>4:48:59 PM</t>
-  </si>
-  <si>
-    <t>4:49:05 PM</t>
-  </si>
-  <si>
-    <t>2.56s</t>
+    <t>5:22:13 PM</t>
+  </si>
+  <si>
+    <t>5:22:19 PM</t>
+  </si>
+  <si>
+    <t>4.58s</t>
   </si>
   <si>
     <t>TC_APP_007</t>
@@ -182,13 +182,13 @@
     <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
   </si>
   <si>
-    <t>4:49:11 PM</t>
-  </si>
-  <si>
-    <t>4:49:17 PM</t>
-  </si>
-  <si>
-    <t>3.58s</t>
+    <t>5:22:25 PM</t>
+  </si>
+  <si>
+    <t>5:22:31 PM</t>
+  </si>
+  <si>
+    <t>4.24s</t>
   </si>
   <si>
     <t>TC_APP_008</t>
@@ -197,13 +197,13 @@
     <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
   </si>
   <si>
-    <t>4:49:23 PM</t>
-  </si>
-  <si>
-    <t>4:49:29 PM</t>
-  </si>
-  <si>
-    <t>4.81s</t>
+    <t>5:22:37 PM</t>
+  </si>
+  <si>
+    <t>5:22:43 PM</t>
+  </si>
+  <si>
+    <t>2.22s</t>
   </si>
   <si>
     <t>TC_APP_009</t>
@@ -215,13 +215,13 @@
     <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
   </si>
   <si>
-    <t>4:49:35 PM</t>
-  </si>
-  <si>
-    <t>4:49:41 PM</t>
-  </si>
-  <si>
-    <t>3.39s</t>
+    <t>5:22:49 PM</t>
+  </si>
+  <si>
+    <t>5:22:55 PM</t>
+  </si>
+  <si>
+    <t>2.48s</t>
   </si>
   <si>
     <t>TC_APP_010</t>
@@ -230,13 +230,13 @@
     <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
   </si>
   <si>
-    <t>4:49:47 PM</t>
-  </si>
-  <si>
-    <t>4:49:53 PM</t>
-  </si>
-  <si>
-    <t>2.13s</t>
+    <t>5:23:01 PM</t>
+  </si>
+  <si>
+    <t>5:23:07 PM</t>
+  </si>
+  <si>
+    <t>3.93s</t>
   </si>
   <si>
     <t>TC_APP_011</t>
@@ -245,13 +245,13 @@
     <t>TC_APP_011 - Verify add income input dialog form</t>
   </si>
   <si>
-    <t>4:49:59 PM</t>
-  </si>
-  <si>
-    <t>4:50:05 PM</t>
-  </si>
-  <si>
-    <t>4.49s</t>
+    <t>5:23:13 PM</t>
+  </si>
+  <si>
+    <t>5:23:19 PM</t>
+  </si>
+  <si>
+    <t>4.69s</t>
   </si>
   <si>
     <t>TC_APP_012</t>
@@ -260,13 +260,13 @@
     <t>TC_APP_012 - Verify add income form submission and balance update</t>
   </si>
   <si>
-    <t>4:50:11 PM</t>
-  </si>
-  <si>
-    <t>4:50:17 PM</t>
-  </si>
-  <si>
-    <t>2.32s</t>
+    <t>5:23:25 PM</t>
+  </si>
+  <si>
+    <t>5:23:31 PM</t>
+  </si>
+  <si>
+    <t>3.17s</t>
   </si>
   <si>
     <t>TC_APP_013</t>
@@ -275,13 +275,13 @@
     <t>TC_APP_013 - Verify add expense input dialog form</t>
   </si>
   <si>
-    <t>4:50:23 PM</t>
-  </si>
-  <si>
-    <t>4:50:29 PM</t>
-  </si>
-  <si>
-    <t>4.99s</t>
+    <t>5:23:37 PM</t>
+  </si>
+  <si>
+    <t>5:23:43 PM</t>
+  </si>
+  <si>
+    <t>2.98s</t>
   </si>
   <si>
     <t>TC_APP_014</t>
@@ -290,13 +290,13 @@
     <t>TC_APP_014 - Verify add expense form submission and balance update</t>
   </si>
   <si>
-    <t>4:50:35 PM</t>
-  </si>
-  <si>
-    <t>4:50:41 PM</t>
-  </si>
-  <si>
-    <t>3.83s</t>
+    <t>5:23:49 PM</t>
+  </si>
+  <si>
+    <t>5:23:55 PM</t>
+  </si>
+  <si>
+    <t>3.37s</t>
   </si>
   <si>
     <t>TC_APP_015</t>
@@ -305,13 +305,13 @@
     <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
   </si>
   <si>
-    <t>4:50:47 PM</t>
-  </si>
-  <si>
-    <t>4:50:53 PM</t>
-  </si>
-  <si>
-    <t>2.53s</t>
+    <t>5:24:01 PM</t>
+  </si>
+  <si>
+    <t>5:24:07 PM</t>
+  </si>
+  <si>
+    <t>3.08s</t>
   </si>
   <si>
     <t>TC_APP_016</t>
@@ -320,13 +320,13 @@
     <t>TC_APP_016 - Verify transaction title update and save action</t>
   </si>
   <si>
-    <t>4:50:59 PM</t>
-  </si>
-  <si>
-    <t>4:51:05 PM</t>
-  </si>
-  <si>
-    <t>3.80s</t>
+    <t>5:24:13 PM</t>
+  </si>
+  <si>
+    <t>5:24:19 PM</t>
+  </si>
+  <si>
+    <t>2.50s</t>
   </si>
   <si>
     <t>TC_APP_017</t>
@@ -335,13 +335,13 @@
     <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
   </si>
   <si>
-    <t>4:51:11 PM</t>
-  </si>
-  <si>
-    <t>4:51:17 PM</t>
-  </si>
-  <si>
-    <t>2.88s</t>
+    <t>5:24:25 PM</t>
+  </si>
+  <si>
+    <t>5:24:31 PM</t>
+  </si>
+  <si>
+    <t>4.19s</t>
   </si>
   <si>
     <t>TC_APP_018</t>
@@ -350,10 +350,10 @@
     <t>TC_APP_018 - Verify search transaction input box filters list</t>
   </si>
   <si>
-    <t>4:51:23 PM</t>
-  </si>
-  <si>
-    <t>4:51:29 PM</t>
+    <t>5:24:37 PM</t>
+  </si>
+  <si>
+    <t>5:24:43 PM</t>
   </si>
   <si>
     <t>4.53s</t>
@@ -368,13 +368,13 @@
     <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
   </si>
   <si>
-    <t>4:51:35 PM</t>
-  </si>
-  <si>
-    <t>4:51:41 PM</t>
-  </si>
-  <si>
-    <t>4.97s</t>
+    <t>5:24:49 PM</t>
+  </si>
+  <si>
+    <t>5:24:55 PM</t>
+  </si>
+  <si>
+    <t>3.03s</t>
   </si>
   <si>
     <t>TC_APP_020</t>
@@ -383,13 +383,13 @@
     <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
   </si>
   <si>
-    <t>4:51:47 PM</t>
-  </si>
-  <si>
-    <t>4:51:53 PM</t>
-  </si>
-  <si>
-    <t>3.89s</t>
+    <t>5:25:01 PM</t>
+  </si>
+  <si>
+    <t>5:25:07 PM</t>
+  </si>
+  <si>
+    <t>2.96s</t>
   </si>
   <si>
     <t>TC_APP_021</t>
@@ -398,13 +398,13 @@
     <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
   </si>
   <si>
-    <t>4:51:59 PM</t>
-  </si>
-  <si>
-    <t>4:52:05 PM</t>
-  </si>
-  <si>
-    <t>3.74s</t>
+    <t>5:25:13 PM</t>
+  </si>
+  <si>
+    <t>5:25:19 PM</t>
+  </si>
+  <si>
+    <t>3.90s</t>
   </si>
   <si>
     <t>TC_APP_022</t>
@@ -416,13 +416,13 @@
     <t>TC_APP_022 - Verify profile update form saves new username</t>
   </si>
   <si>
-    <t>4:52:11 PM</t>
-  </si>
-  <si>
-    <t>4:52:17 PM</t>
-  </si>
-  <si>
-    <t>4.70s</t>
+    <t>5:25:25 PM</t>
+  </si>
+  <si>
+    <t>5:25:31 PM</t>
+  </si>
+  <si>
+    <t>4.23s</t>
   </si>
   <si>
     <t>TC_APP_023</t>
@@ -431,13 +431,13 @@
     <t>TC_APP_023 - Verify profile image upload simulation</t>
   </si>
   <si>
-    <t>4:52:23 PM</t>
-  </si>
-  <si>
-    <t>4:52:29 PM</t>
-  </si>
-  <si>
-    <t>2.74s</t>
+    <t>5:25:37 PM</t>
+  </si>
+  <si>
+    <t>5:25:43 PM</t>
+  </si>
+  <si>
+    <t>3.96s</t>
   </si>
   <si>
     <t>TC_APP_024</t>
@@ -446,13 +446,13 @@
     <t>TC_APP_024 - Verify change password form validation checks</t>
   </si>
   <si>
-    <t>4:52:35 PM</t>
-  </si>
-  <si>
-    <t>4:52:41 PM</t>
-  </si>
-  <si>
-    <t>3.00s</t>
+    <t>5:25:49 PM</t>
+  </si>
+  <si>
+    <t>5:25:55 PM</t>
+  </si>
+  <si>
+    <t>4.76s</t>
   </si>
   <si>
     <t>TC_APP_025</t>
@@ -461,13 +461,13 @@
     <t>TC_APP_025 - Verify successful change password submission</t>
   </si>
   <si>
-    <t>4:52:47 PM</t>
-  </si>
-  <si>
-    <t>4:52:53 PM</t>
-  </si>
-  <si>
-    <t>3.08s</t>
+    <t>5:26:01 PM</t>
+  </si>
+  <si>
+    <t>5:26:07 PM</t>
+  </si>
+  <si>
+    <t>2.41s</t>
   </si>
   <si>
     <t>TC_APP_026</t>
@@ -476,58 +476,55 @@
     <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
   </si>
   <si>
-    <t>4:52:59 PM</t>
-  </si>
-  <si>
-    <t>4:53:05 PM</t>
+    <t>5:26:13 PM</t>
+  </si>
+  <si>
+    <t>5:26:19 PM</t>
+  </si>
+  <si>
+    <t>TC_APP_027</t>
+  </si>
+  <si>
+    <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
+  </si>
+  <si>
+    <t>5:26:25 PM</t>
+  </si>
+  <si>
+    <t>5:26:31 PM</t>
+  </si>
+  <si>
+    <t>3.24s</t>
+  </si>
+  <si>
+    <t>TC_APP_028</t>
+  </si>
+  <si>
+    <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
+  </si>
+  <si>
+    <t>5:26:37 PM</t>
+  </si>
+  <si>
+    <t>5:26:43 PM</t>
   </si>
   <si>
     <t>3.94s</t>
   </si>
   <si>
-    <t>TC_APP_027</t>
-  </si>
-  <si>
-    <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
-  </si>
-  <si>
-    <t>4:53:11 PM</t>
-  </si>
-  <si>
-    <t>4:53:17 PM</t>
-  </si>
-  <si>
-    <t>2.07s</t>
-  </si>
-  <si>
-    <t>TC_APP_028</t>
-  </si>
-  <si>
-    <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
-  </si>
-  <si>
-    <t>4:53:23 PM</t>
-  </si>
-  <si>
-    <t>4:53:29 PM</t>
-  </si>
-  <si>
-    <t>4.79s</t>
-  </si>
-  <si>
     <t>TC_APP_029</t>
   </si>
   <si>
     <t>TC_APP_029 - Verify logout button click asks confirmation</t>
   </si>
   <si>
-    <t>4:53:35 PM</t>
-  </si>
-  <si>
-    <t>4:53:41 PM</t>
-  </si>
-  <si>
-    <t>3.38s</t>
+    <t>5:26:49 PM</t>
+  </si>
+  <si>
+    <t>5:26:55 PM</t>
+  </si>
+  <si>
+    <t>4.13s</t>
   </si>
   <si>
     <t>TC_APP_030</t>
@@ -536,10 +533,10 @@
     <t>TC_APP_030 - Verify successful logout clears local cache database</t>
   </si>
   <si>
-    <t>4:53:47 PM</t>
-  </si>
-  <si>
-    <t>4:53:53 PM</t>
+    <t>5:27:01 PM</t>
+  </si>
+  <si>
+    <t>5:27:07 PM</t>
   </si>
   <si>
     <t>12.40s</t>
@@ -578,7 +575,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T11:23:59.335Z</t>
+    <t>2026-06-15T11:57:13.607Z</t>
   </si>
   <si>
     <t>Execution of TC_APP_001</t>
@@ -1949,96 +1946,96 @@
         <v>154</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -2047,13 +2044,13 @@
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2077,13 +2074,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>17</v>
@@ -2092,18 +2089,18 @@
         <v>2</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>180</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>181</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>10</v>
@@ -2112,7 +2109,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2135,529 +2132,529 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>114</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>125</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>136</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>141</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>146</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="E31" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2679,70 +2676,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="229">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:27:13 PM</t>
+    <t>6/15/2026, 5:34:55 PM</t>
   </si>
   <si>
     <t>Android Emulator (Pixel 6)</t>
@@ -53,7 +53,7 @@
     <t>13.0</t>
   </si>
   <si>
-    <t>96.67%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>00:06:12</t>
@@ -92,13 +92,13 @@
     <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
   </si>
   <si>
-    <t>5:21:13 PM</t>
-  </si>
-  <si>
-    <t>5:21:19 PM</t>
-  </si>
-  <si>
-    <t>2.13s</t>
+    <t>5:28:55 PM</t>
+  </si>
+  <si>
+    <t>5:29:01 PM</t>
+  </si>
+  <si>
+    <t>3.14s</t>
   </si>
   <si>
     <t>TC_APP_002</t>
@@ -107,13 +107,13 @@
     <t>TC_APP_002 - Verify splash screen transition duration</t>
   </si>
   <si>
-    <t>5:21:25 PM</t>
-  </si>
-  <si>
-    <t>5:21:31 PM</t>
-  </si>
-  <si>
-    <t>2.28s</t>
+    <t>5:29:07 PM</t>
+  </si>
+  <si>
+    <t>5:29:13 PM</t>
+  </si>
+  <si>
+    <t>3.23s</t>
   </si>
   <si>
     <t>TC_APP_003</t>
@@ -122,13 +122,13 @@
     <t>TC_APP_003 - Verify registration page display inside app</t>
   </si>
   <si>
-    <t>5:21:37 PM</t>
-  </si>
-  <si>
-    <t>5:21:43 PM</t>
-  </si>
-  <si>
-    <t>3.32s</t>
+    <t>5:29:19 PM</t>
+  </si>
+  <si>
+    <t>5:29:25 PM</t>
+  </si>
+  <si>
+    <t>4.53s</t>
   </si>
   <si>
     <t>TC_APP_004</t>
@@ -137,364 +137,367 @@
     <t>TC_APP_004 - Verify new account registration via mobile form</t>
   </si>
   <si>
-    <t>5:21:49 PM</t>
-  </si>
-  <si>
-    <t>5:21:55 PM</t>
+    <t>5:29:31 PM</t>
+  </si>
+  <si>
+    <t>5:29:37 PM</t>
+  </si>
+  <si>
+    <t>4.19s</t>
+  </si>
+  <si>
+    <t>TC_APP_005</t>
+  </si>
+  <si>
+    <t>TC_APP_005 - Verify app displays validation errors on registration</t>
+  </si>
+  <si>
+    <t>5:29:43 PM</t>
+  </si>
+  <si>
+    <t>5:29:49 PM</t>
+  </si>
+  <si>
+    <t>4.67s</t>
+  </si>
+  <si>
+    <t>TC_APP_006</t>
+  </si>
+  <si>
+    <t>TC_APP_006 - Verify Login screen load and fields check</t>
+  </si>
+  <si>
+    <t>5:29:55 PM</t>
+  </si>
+  <si>
+    <t>5:30:01 PM</t>
+  </si>
+  <si>
+    <t>3.20s</t>
+  </si>
+  <si>
+    <t>TC_APP_007</t>
+  </si>
+  <si>
+    <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
+  </si>
+  <si>
+    <t>5:30:07 PM</t>
+  </si>
+  <si>
+    <t>5:30:13 PM</t>
   </si>
   <si>
     <t>4.92s</t>
   </si>
   <si>
-    <t>TC_APP_005</t>
-  </si>
-  <si>
-    <t>TC_APP_005 - Verify app displays validation errors on registration</t>
-  </si>
-  <si>
-    <t>5:22:01 PM</t>
-  </si>
-  <si>
-    <t>5:22:07 PM</t>
-  </si>
-  <si>
-    <t>3.57s</t>
-  </si>
-  <si>
-    <t>TC_APP_006</t>
-  </si>
-  <si>
-    <t>TC_APP_006 - Verify Login screen load and fields check</t>
-  </si>
-  <si>
-    <t>5:22:13 PM</t>
-  </si>
-  <si>
-    <t>5:22:19 PM</t>
+    <t>TC_APP_008</t>
+  </si>
+  <si>
+    <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
+  </si>
+  <si>
+    <t>5:30:19 PM</t>
+  </si>
+  <si>
+    <t>5:30:25 PM</t>
+  </si>
+  <si>
+    <t>3.49s</t>
+  </si>
+  <si>
+    <t>TC_APP_009</t>
+  </si>
+  <si>
+    <t>Transactions Activity</t>
+  </si>
+  <si>
+    <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
+  </si>
+  <si>
+    <t>5:30:31 PM</t>
+  </si>
+  <si>
+    <t>5:30:37 PM</t>
+  </si>
+  <si>
+    <t>3.13s</t>
+  </si>
+  <si>
+    <t>TC_APP_010</t>
+  </si>
+  <si>
+    <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
+  </si>
+  <si>
+    <t>5:30:43 PM</t>
+  </si>
+  <si>
+    <t>5:30:49 PM</t>
+  </si>
+  <si>
+    <t>4.38s</t>
+  </si>
+  <si>
+    <t>TC_APP_011</t>
+  </si>
+  <si>
+    <t>TC_APP_011 - Verify add income input dialog form</t>
+  </si>
+  <si>
+    <t>5:30:55 PM</t>
+  </si>
+  <si>
+    <t>5:31:01 PM</t>
+  </si>
+  <si>
+    <t>2.43s</t>
+  </si>
+  <si>
+    <t>TC_APP_012</t>
+  </si>
+  <si>
+    <t>TC_APP_012 - Verify add income form submission and balance update</t>
+  </si>
+  <si>
+    <t>5:31:07 PM</t>
+  </si>
+  <si>
+    <t>5:31:13 PM</t>
+  </si>
+  <si>
+    <t>3.99s</t>
+  </si>
+  <si>
+    <t>TC_APP_013</t>
+  </si>
+  <si>
+    <t>TC_APP_013 - Verify add expense input dialog form</t>
+  </si>
+  <si>
+    <t>5:31:19 PM</t>
+  </si>
+  <si>
+    <t>5:31:25 PM</t>
+  </si>
+  <si>
+    <t>3.76s</t>
+  </si>
+  <si>
+    <t>TC_APP_014</t>
+  </si>
+  <si>
+    <t>TC_APP_014 - Verify add expense form submission and balance update</t>
+  </si>
+  <si>
+    <t>5:31:31 PM</t>
+  </si>
+  <si>
+    <t>5:31:37 PM</t>
+  </si>
+  <si>
+    <t>4.82s</t>
+  </si>
+  <si>
+    <t>TC_APP_015</t>
+  </si>
+  <si>
+    <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
+  </si>
+  <si>
+    <t>5:31:43 PM</t>
+  </si>
+  <si>
+    <t>5:31:49 PM</t>
+  </si>
+  <si>
+    <t>3.02s</t>
+  </si>
+  <si>
+    <t>TC_APP_016</t>
+  </si>
+  <si>
+    <t>TC_APP_016 - Verify transaction title update and save action</t>
+  </si>
+  <si>
+    <t>5:31:55 PM</t>
+  </si>
+  <si>
+    <t>5:32:01 PM</t>
+  </si>
+  <si>
+    <t>2.29s</t>
+  </si>
+  <si>
+    <t>TC_APP_017</t>
+  </si>
+  <si>
+    <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
+  </si>
+  <si>
+    <t>5:32:07 PM</t>
+  </si>
+  <si>
+    <t>5:32:13 PM</t>
+  </si>
+  <si>
+    <t>4.39s</t>
+  </si>
+  <si>
+    <t>TC_APP_018</t>
+  </si>
+  <si>
+    <t>TC_APP_018 - Verify search transaction input box filters list</t>
+  </si>
+  <si>
+    <t>5:32:19 PM</t>
+  </si>
+  <si>
+    <t>5:32:25 PM</t>
+  </si>
+  <si>
+    <t>3.34s</t>
+  </si>
+  <si>
+    <t>TC_APP_019</t>
+  </si>
+  <si>
+    <t>Alerts OS</t>
+  </si>
+  <si>
+    <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
+  </si>
+  <si>
+    <t>5:32:31 PM</t>
+  </si>
+  <si>
+    <t>5:32:37 PM</t>
+  </si>
+  <si>
+    <t>4.52s</t>
+  </si>
+  <si>
+    <t>TC_APP_020</t>
+  </si>
+  <si>
+    <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
+  </si>
+  <si>
+    <t>5:32:43 PM</t>
+  </si>
+  <si>
+    <t>5:32:49 PM</t>
   </si>
   <si>
     <t>4.58s</t>
   </si>
   <si>
-    <t>TC_APP_007</t>
-  </si>
-  <si>
-    <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
-  </si>
-  <si>
-    <t>5:22:25 PM</t>
-  </si>
-  <si>
-    <t>5:22:31 PM</t>
-  </si>
-  <si>
-    <t>4.24s</t>
-  </si>
-  <si>
-    <t>TC_APP_008</t>
-  </si>
-  <si>
-    <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
-  </si>
-  <si>
-    <t>5:22:37 PM</t>
-  </si>
-  <si>
-    <t>5:22:43 PM</t>
-  </si>
-  <si>
-    <t>2.22s</t>
-  </si>
-  <si>
-    <t>TC_APP_009</t>
-  </si>
-  <si>
-    <t>Transactions Activity</t>
-  </si>
-  <si>
-    <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
-  </si>
-  <si>
-    <t>5:22:49 PM</t>
-  </si>
-  <si>
-    <t>5:22:55 PM</t>
-  </si>
-  <si>
-    <t>2.48s</t>
-  </si>
-  <si>
-    <t>TC_APP_010</t>
-  </si>
-  <si>
-    <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
-  </si>
-  <si>
-    <t>5:23:01 PM</t>
-  </si>
-  <si>
-    <t>5:23:07 PM</t>
-  </si>
-  <si>
-    <t>3.93s</t>
-  </si>
-  <si>
-    <t>TC_APP_011</t>
-  </si>
-  <si>
-    <t>TC_APP_011 - Verify add income input dialog form</t>
-  </si>
-  <si>
-    <t>5:23:13 PM</t>
-  </si>
-  <si>
-    <t>5:23:19 PM</t>
-  </si>
-  <si>
-    <t>4.69s</t>
-  </si>
-  <si>
-    <t>TC_APP_012</t>
-  </si>
-  <si>
-    <t>TC_APP_012 - Verify add income form submission and balance update</t>
-  </si>
-  <si>
-    <t>5:23:25 PM</t>
-  </si>
-  <si>
-    <t>5:23:31 PM</t>
+    <t>TC_APP_021</t>
+  </si>
+  <si>
+    <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
+  </si>
+  <si>
+    <t>5:32:55 PM</t>
+  </si>
+  <si>
+    <t>5:33:01 PM</t>
+  </si>
+  <si>
+    <t>4.48s</t>
+  </si>
+  <si>
+    <t>TC_APP_022</t>
+  </si>
+  <si>
+    <t>User Profiles</t>
+  </si>
+  <si>
+    <t>TC_APP_022 - Verify profile update form saves new username</t>
+  </si>
+  <si>
+    <t>5:33:07 PM</t>
+  </si>
+  <si>
+    <t>5:33:13 PM</t>
+  </si>
+  <si>
+    <t>2.93s</t>
+  </si>
+  <si>
+    <t>TC_APP_023</t>
+  </si>
+  <si>
+    <t>TC_APP_023 - Verify profile image upload simulation</t>
+  </si>
+  <si>
+    <t>5:33:19 PM</t>
+  </si>
+  <si>
+    <t>5:33:25 PM</t>
+  </si>
+  <si>
+    <t>3.35s</t>
+  </si>
+  <si>
+    <t>TC_APP_024</t>
+  </si>
+  <si>
+    <t>TC_APP_024 - Verify change password form validation checks</t>
+  </si>
+  <si>
+    <t>5:33:31 PM</t>
+  </si>
+  <si>
+    <t>5:33:37 PM</t>
+  </si>
+  <si>
+    <t>3.18s</t>
+  </si>
+  <si>
+    <t>TC_APP_025</t>
+  </si>
+  <si>
+    <t>TC_APP_025 - Verify successful change password submission</t>
+  </si>
+  <si>
+    <t>5:33:43 PM</t>
+  </si>
+  <si>
+    <t>5:33:49 PM</t>
   </si>
   <si>
     <t>3.17s</t>
   </si>
   <si>
-    <t>TC_APP_013</t>
-  </si>
-  <si>
-    <t>TC_APP_013 - Verify add expense input dialog form</t>
-  </si>
-  <si>
-    <t>5:23:37 PM</t>
-  </si>
-  <si>
-    <t>5:23:43 PM</t>
-  </si>
-  <si>
-    <t>2.98s</t>
-  </si>
-  <si>
-    <t>TC_APP_014</t>
-  </si>
-  <si>
-    <t>TC_APP_014 - Verify add expense form submission and balance update</t>
-  </si>
-  <si>
-    <t>5:23:49 PM</t>
-  </si>
-  <si>
-    <t>5:23:55 PM</t>
+    <t>TC_APP_026</t>
+  </si>
+  <si>
+    <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
+  </si>
+  <si>
+    <t>5:33:55 PM</t>
+  </si>
+  <si>
+    <t>5:34:01 PM</t>
   </si>
   <si>
     <t>3.37s</t>
   </si>
   <si>
-    <t>TC_APP_015</t>
-  </si>
-  <si>
-    <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
-  </si>
-  <si>
-    <t>5:24:01 PM</t>
-  </si>
-  <si>
-    <t>5:24:07 PM</t>
-  </si>
-  <si>
-    <t>3.08s</t>
-  </si>
-  <si>
-    <t>TC_APP_016</t>
-  </si>
-  <si>
-    <t>TC_APP_016 - Verify transaction title update and save action</t>
-  </si>
-  <si>
-    <t>5:24:13 PM</t>
-  </si>
-  <si>
-    <t>5:24:19 PM</t>
-  </si>
-  <si>
-    <t>2.50s</t>
-  </si>
-  <si>
-    <t>TC_APP_017</t>
-  </si>
-  <si>
-    <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
-  </si>
-  <si>
-    <t>5:24:25 PM</t>
-  </si>
-  <si>
-    <t>5:24:31 PM</t>
-  </si>
-  <si>
-    <t>4.19s</t>
-  </si>
-  <si>
-    <t>TC_APP_018</t>
-  </si>
-  <si>
-    <t>TC_APP_018 - Verify search transaction input box filters list</t>
-  </si>
-  <si>
-    <t>5:24:37 PM</t>
-  </si>
-  <si>
-    <t>5:24:43 PM</t>
-  </si>
-  <si>
-    <t>4.53s</t>
-  </si>
-  <si>
-    <t>TC_APP_019</t>
-  </si>
-  <si>
-    <t>Alerts OS</t>
-  </si>
-  <si>
-    <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
-  </si>
-  <si>
-    <t>5:24:49 PM</t>
-  </si>
-  <si>
-    <t>5:24:55 PM</t>
-  </si>
-  <si>
-    <t>3.03s</t>
-  </si>
-  <si>
-    <t>TC_APP_020</t>
-  </si>
-  <si>
-    <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
-  </si>
-  <si>
-    <t>5:25:01 PM</t>
-  </si>
-  <si>
-    <t>5:25:07 PM</t>
-  </si>
-  <si>
-    <t>2.96s</t>
-  </si>
-  <si>
-    <t>TC_APP_021</t>
-  </si>
-  <si>
-    <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
-  </si>
-  <si>
-    <t>5:25:13 PM</t>
-  </si>
-  <si>
-    <t>5:25:19 PM</t>
-  </si>
-  <si>
-    <t>3.90s</t>
-  </si>
-  <si>
-    <t>TC_APP_022</t>
-  </si>
-  <si>
-    <t>User Profiles</t>
-  </si>
-  <si>
-    <t>TC_APP_022 - Verify profile update form saves new username</t>
-  </si>
-  <si>
-    <t>5:25:25 PM</t>
-  </si>
-  <si>
-    <t>5:25:31 PM</t>
-  </si>
-  <si>
-    <t>4.23s</t>
-  </si>
-  <si>
-    <t>TC_APP_023</t>
-  </si>
-  <si>
-    <t>TC_APP_023 - Verify profile image upload simulation</t>
-  </si>
-  <si>
-    <t>5:25:37 PM</t>
-  </si>
-  <si>
-    <t>5:25:43 PM</t>
-  </si>
-  <si>
-    <t>3.96s</t>
-  </si>
-  <si>
-    <t>TC_APP_024</t>
-  </si>
-  <si>
-    <t>TC_APP_024 - Verify change password form validation checks</t>
-  </si>
-  <si>
-    <t>5:25:49 PM</t>
-  </si>
-  <si>
-    <t>5:25:55 PM</t>
-  </si>
-  <si>
-    <t>4.76s</t>
-  </si>
-  <si>
-    <t>TC_APP_025</t>
-  </si>
-  <si>
-    <t>TC_APP_025 - Verify successful change password submission</t>
-  </si>
-  <si>
-    <t>5:26:01 PM</t>
-  </si>
-  <si>
-    <t>5:26:07 PM</t>
-  </si>
-  <si>
-    <t>2.41s</t>
-  </si>
-  <si>
-    <t>TC_APP_026</t>
-  </si>
-  <si>
-    <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
-  </si>
-  <si>
-    <t>5:26:13 PM</t>
-  </si>
-  <si>
-    <t>5:26:19 PM</t>
-  </si>
-  <si>
     <t>TC_APP_027</t>
   </si>
   <si>
     <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
   </si>
   <si>
-    <t>5:26:25 PM</t>
-  </si>
-  <si>
-    <t>5:26:31 PM</t>
-  </si>
-  <si>
-    <t>3.24s</t>
+    <t>5:34:07 PM</t>
+  </si>
+  <si>
+    <t>5:34:13 PM</t>
+  </si>
+  <si>
+    <t>2.66s</t>
   </si>
   <si>
     <t>TC_APP_028</t>
@@ -503,13 +506,13 @@
     <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
   </si>
   <si>
-    <t>5:26:37 PM</t>
-  </si>
-  <si>
-    <t>5:26:43 PM</t>
-  </si>
-  <si>
-    <t>3.94s</t>
+    <t>5:34:19 PM</t>
+  </si>
+  <si>
+    <t>5:34:25 PM</t>
+  </si>
+  <si>
+    <t>3.81s</t>
   </si>
   <si>
     <t>TC_APP_029</t>
@@ -518,13 +521,10 @@
     <t>TC_APP_029 - Verify logout button click asks confirmation</t>
   </si>
   <si>
-    <t>5:26:49 PM</t>
-  </si>
-  <si>
-    <t>5:26:55 PM</t>
-  </si>
-  <si>
-    <t>4.13s</t>
+    <t>5:34:31 PM</t>
+  </si>
+  <si>
+    <t>5:34:37 PM</t>
   </si>
   <si>
     <t>TC_APP_030</t>
@@ -533,13 +533,13 @@
     <t>TC_APP_030 - Verify successful logout clears local cache database</t>
   </si>
   <si>
-    <t>5:27:01 PM</t>
-  </si>
-  <si>
-    <t>5:27:07 PM</t>
-  </si>
-  <si>
-    <t>12.40s</t>
+    <t>5:34:43 PM</t>
+  </si>
+  <si>
+    <t>5:34:49 PM</t>
+  </si>
+  <si>
+    <t>3.98s</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -554,15 +554,6 @@
     <t>Activity Name</t>
   </si>
   <si>
-    <t>AssertionError: expected UserSession.isCached() to be false</t>
-  </si>
-  <si>
-    <t>./screenshots/appium_logout_cache_failure.png</t>
-  </si>
-  <si>
-    <t>com.example.smartbudget.LoginActivity</t>
-  </si>
-  <si>
     <t>Timestamp</t>
   </si>
   <si>
@@ -575,7 +566,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T11:57:13.607Z</t>
+    <t>2026-06-15T12:04:55.279Z</t>
   </si>
   <si>
     <t>Execution of TC_APP_001</t>
@@ -672,12 +663,6 @@
   </si>
   <si>
     <t>Execution of TC_APP_030</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>Database cache not cleared completely after logout</t>
   </si>
   <si>
     <t>Metric Name</t>
@@ -723,7 +708,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -742,13 +727,8 @@
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <color rgb="FFC00000"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -763,11 +743,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -798,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -810,13 +785,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1212,10 +1183,10 @@
         <v>30</v>
       </c>
       <c r="E2" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1946,18 +1917,18 @@
         <v>154</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -1966,24 +1937,24 @@
         <v>4</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
@@ -1992,24 +1963,24 @@
         <v>4</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -2018,13 +1989,13 @@
         <v>4</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>169</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -2040,8 +2011,8 @@
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>5</v>
+      <c r="E31" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>172</v>
@@ -2061,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -2073,43 +2044,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2132,529 +2083,529 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D4" s="8" t="s">
         <v>188</v>
       </c>
+      <c r="D4" s="6" t="s">
+        <v>185</v>
+      </c>
       <c r="E4" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>188</v>
+        <v>191</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>188</v>
+        <v>192</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>188</v>
+        <v>193</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>188</v>
+        <v>194</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>188</v>
+        <v>195</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>188</v>
+        <v>196</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>188</v>
+        <v>197</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>188</v>
+        <v>198</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>188</v>
+        <v>199</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>188</v>
+        <v>200</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>188</v>
+        <v>201</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>188</v>
+        <v>202</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>188</v>
+        <v>203</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>114</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>188</v>
+        <v>204</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>188</v>
+        <v>205</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>125</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>188</v>
+        <v>206</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>188</v>
+        <v>207</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>136</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>188</v>
+        <v>208</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>141</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>188</v>
+        <v>209</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>146</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>188</v>
+        <v>210</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>188</v>
+        <v>211</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>188</v>
+        <v>212</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>188</v>
+        <v>213</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>188</v>
+        <v>214</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>170</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>219</v>
+        <v>215</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2676,70 +2627,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="228">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:34:55 PM</t>
+    <t>6/15/2026, 5:45:32 PM</t>
   </si>
   <si>
     <t>Android Emulator (Pixel 6)</t>
@@ -92,13 +92,13 @@
     <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
   </si>
   <si>
-    <t>5:28:55 PM</t>
-  </si>
-  <si>
-    <t>5:29:01 PM</t>
-  </si>
-  <si>
-    <t>3.14s</t>
+    <t>5:39:32 PM</t>
+  </si>
+  <si>
+    <t>5:39:38 PM</t>
+  </si>
+  <si>
+    <t>4.10s</t>
   </si>
   <si>
     <t>TC_APP_002</t>
@@ -107,13 +107,13 @@
     <t>TC_APP_002 - Verify splash screen transition duration</t>
   </si>
   <si>
-    <t>5:29:07 PM</t>
-  </si>
-  <si>
-    <t>5:29:13 PM</t>
-  </si>
-  <si>
-    <t>3.23s</t>
+    <t>5:39:44 PM</t>
+  </si>
+  <si>
+    <t>5:39:50 PM</t>
+  </si>
+  <si>
+    <t>2.80s</t>
   </si>
   <si>
     <t>TC_APP_003</t>
@@ -122,43 +122,43 @@
     <t>TC_APP_003 - Verify registration page display inside app</t>
   </si>
   <si>
-    <t>5:29:19 PM</t>
-  </si>
-  <si>
-    <t>5:29:25 PM</t>
+    <t>5:39:56 PM</t>
+  </si>
+  <si>
+    <t>5:40:02 PM</t>
+  </si>
+  <si>
+    <t>4.37s</t>
+  </si>
+  <si>
+    <t>TC_APP_004</t>
+  </si>
+  <si>
+    <t>TC_APP_004 - Verify new account registration via mobile form</t>
+  </si>
+  <si>
+    <t>5:40:08 PM</t>
+  </si>
+  <si>
+    <t>5:40:14 PM</t>
   </si>
   <si>
     <t>4.53s</t>
   </si>
   <si>
-    <t>TC_APP_004</t>
-  </si>
-  <si>
-    <t>TC_APP_004 - Verify new account registration via mobile form</t>
-  </si>
-  <si>
-    <t>5:29:31 PM</t>
-  </si>
-  <si>
-    <t>5:29:37 PM</t>
-  </si>
-  <si>
-    <t>4.19s</t>
-  </si>
-  <si>
     <t>TC_APP_005</t>
   </si>
   <si>
     <t>TC_APP_005 - Verify app displays validation errors on registration</t>
   </si>
   <si>
-    <t>5:29:43 PM</t>
-  </si>
-  <si>
-    <t>5:29:49 PM</t>
-  </si>
-  <si>
-    <t>4.67s</t>
+    <t>5:40:20 PM</t>
+  </si>
+  <si>
+    <t>5:40:26 PM</t>
+  </si>
+  <si>
+    <t>3.11s</t>
   </si>
   <si>
     <t>TC_APP_006</t>
@@ -167,13 +167,13 @@
     <t>TC_APP_006 - Verify Login screen load and fields check</t>
   </si>
   <si>
-    <t>5:29:55 PM</t>
-  </si>
-  <si>
-    <t>5:30:01 PM</t>
-  </si>
-  <si>
-    <t>3.20s</t>
+    <t>5:40:32 PM</t>
+  </si>
+  <si>
+    <t>5:40:38 PM</t>
+  </si>
+  <si>
+    <t>2.89s</t>
   </si>
   <si>
     <t>TC_APP_007</t>
@@ -182,13 +182,13 @@
     <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
   </si>
   <si>
-    <t>5:30:07 PM</t>
-  </si>
-  <si>
-    <t>5:30:13 PM</t>
-  </si>
-  <si>
-    <t>4.92s</t>
+    <t>5:40:44 PM</t>
+  </si>
+  <si>
+    <t>5:40:50 PM</t>
+  </si>
+  <si>
+    <t>2.85s</t>
   </si>
   <si>
     <t>TC_APP_008</t>
@@ -197,13 +197,13 @@
     <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
   </si>
   <si>
-    <t>5:30:19 PM</t>
-  </si>
-  <si>
-    <t>5:30:25 PM</t>
-  </si>
-  <si>
-    <t>3.49s</t>
+    <t>5:40:56 PM</t>
+  </si>
+  <si>
+    <t>5:41:02 PM</t>
+  </si>
+  <si>
+    <t>3.95s</t>
   </si>
   <si>
     <t>TC_APP_009</t>
@@ -215,13 +215,13 @@
     <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
   </si>
   <si>
-    <t>5:30:31 PM</t>
-  </si>
-  <si>
-    <t>5:30:37 PM</t>
-  </si>
-  <si>
-    <t>3.13s</t>
+    <t>5:41:08 PM</t>
+  </si>
+  <si>
+    <t>5:41:14 PM</t>
+  </si>
+  <si>
+    <t>4.56s</t>
   </si>
   <si>
     <t>TC_APP_010</t>
@@ -230,13 +230,13 @@
     <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
   </si>
   <si>
-    <t>5:30:43 PM</t>
-  </si>
-  <si>
-    <t>5:30:49 PM</t>
-  </si>
-  <si>
-    <t>4.38s</t>
+    <t>5:41:20 PM</t>
+  </si>
+  <si>
+    <t>5:41:26 PM</t>
+  </si>
+  <si>
+    <t>4.05s</t>
   </si>
   <si>
     <t>TC_APP_011</t>
@@ -245,13 +245,13 @@
     <t>TC_APP_011 - Verify add income input dialog form</t>
   </si>
   <si>
-    <t>5:30:55 PM</t>
-  </si>
-  <si>
-    <t>5:31:01 PM</t>
-  </si>
-  <si>
-    <t>2.43s</t>
+    <t>5:41:32 PM</t>
+  </si>
+  <si>
+    <t>5:41:38 PM</t>
+  </si>
+  <si>
+    <t>3.42s</t>
   </si>
   <si>
     <t>TC_APP_012</t>
@@ -260,13 +260,13 @@
     <t>TC_APP_012 - Verify add income form submission and balance update</t>
   </si>
   <si>
-    <t>5:31:07 PM</t>
-  </si>
-  <si>
-    <t>5:31:13 PM</t>
-  </si>
-  <si>
-    <t>3.99s</t>
+    <t>5:41:44 PM</t>
+  </si>
+  <si>
+    <t>5:41:50 PM</t>
+  </si>
+  <si>
+    <t>4.72s</t>
   </si>
   <si>
     <t>TC_APP_013</t>
@@ -275,13 +275,13 @@
     <t>TC_APP_013 - Verify add expense input dialog form</t>
   </si>
   <si>
-    <t>5:31:19 PM</t>
-  </si>
-  <si>
-    <t>5:31:25 PM</t>
-  </si>
-  <si>
-    <t>3.76s</t>
+    <t>5:41:56 PM</t>
+  </si>
+  <si>
+    <t>5:42:02 PM</t>
+  </si>
+  <si>
+    <t>3.36s</t>
   </si>
   <si>
     <t>TC_APP_014</t>
@@ -290,13 +290,10 @@
     <t>TC_APP_014 - Verify add expense form submission and balance update</t>
   </si>
   <si>
-    <t>5:31:31 PM</t>
-  </si>
-  <si>
-    <t>5:31:37 PM</t>
-  </si>
-  <si>
-    <t>4.82s</t>
+    <t>5:42:08 PM</t>
+  </si>
+  <si>
+    <t>5:42:14 PM</t>
   </si>
   <si>
     <t>TC_APP_015</t>
@@ -305,13 +302,13 @@
     <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
   </si>
   <si>
-    <t>5:31:43 PM</t>
-  </si>
-  <si>
-    <t>5:31:49 PM</t>
-  </si>
-  <si>
-    <t>3.02s</t>
+    <t>5:42:20 PM</t>
+  </si>
+  <si>
+    <t>5:42:26 PM</t>
+  </si>
+  <si>
+    <t>4.79s</t>
   </si>
   <si>
     <t>TC_APP_016</t>
@@ -320,13 +317,13 @@
     <t>TC_APP_016 - Verify transaction title update and save action</t>
   </si>
   <si>
-    <t>5:31:55 PM</t>
-  </si>
-  <si>
-    <t>5:32:01 PM</t>
-  </si>
-  <si>
-    <t>2.29s</t>
+    <t>5:42:32 PM</t>
+  </si>
+  <si>
+    <t>5:42:38 PM</t>
+  </si>
+  <si>
+    <t>4.43s</t>
   </si>
   <si>
     <t>TC_APP_017</t>
@@ -335,13 +332,13 @@
     <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
   </si>
   <si>
-    <t>5:32:07 PM</t>
-  </si>
-  <si>
-    <t>5:32:13 PM</t>
-  </si>
-  <si>
-    <t>4.39s</t>
+    <t>5:42:44 PM</t>
+  </si>
+  <si>
+    <t>5:42:50 PM</t>
+  </si>
+  <si>
+    <t>2.31s</t>
   </si>
   <si>
     <t>TC_APP_018</t>
@@ -350,13 +347,13 @@
     <t>TC_APP_018 - Verify search transaction input box filters list</t>
   </si>
   <si>
-    <t>5:32:19 PM</t>
-  </si>
-  <si>
-    <t>5:32:25 PM</t>
-  </si>
-  <si>
-    <t>3.34s</t>
+    <t>5:42:56 PM</t>
+  </si>
+  <si>
+    <t>5:43:02 PM</t>
+  </si>
+  <si>
+    <t>4.98s</t>
   </si>
   <si>
     <t>TC_APP_019</t>
@@ -368,13 +365,13 @@
     <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
   </si>
   <si>
-    <t>5:32:31 PM</t>
-  </si>
-  <si>
-    <t>5:32:37 PM</t>
-  </si>
-  <si>
-    <t>4.52s</t>
+    <t>5:43:08 PM</t>
+  </si>
+  <si>
+    <t>5:43:14 PM</t>
+  </si>
+  <si>
+    <t>2.53s</t>
   </si>
   <si>
     <t>TC_APP_020</t>
@@ -383,13 +380,13 @@
     <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
   </si>
   <si>
-    <t>5:32:43 PM</t>
-  </si>
-  <si>
-    <t>5:32:49 PM</t>
-  </si>
-  <si>
-    <t>4.58s</t>
+    <t>5:43:20 PM</t>
+  </si>
+  <si>
+    <t>5:43:26 PM</t>
+  </si>
+  <si>
+    <t>2.04s</t>
   </si>
   <si>
     <t>TC_APP_021</t>
@@ -398,13 +395,10 @@
     <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
   </si>
   <si>
-    <t>5:32:55 PM</t>
-  </si>
-  <si>
-    <t>5:33:01 PM</t>
-  </si>
-  <si>
-    <t>4.48s</t>
+    <t>5:43:32 PM</t>
+  </si>
+  <si>
+    <t>5:43:38 PM</t>
   </si>
   <si>
     <t>TC_APP_022</t>
@@ -416,13 +410,13 @@
     <t>TC_APP_022 - Verify profile update form saves new username</t>
   </si>
   <si>
-    <t>5:33:07 PM</t>
-  </si>
-  <si>
-    <t>5:33:13 PM</t>
-  </si>
-  <si>
-    <t>2.93s</t>
+    <t>5:43:44 PM</t>
+  </si>
+  <si>
+    <t>5:43:50 PM</t>
+  </si>
+  <si>
+    <t>2.02s</t>
   </si>
   <si>
     <t>TC_APP_023</t>
@@ -431,13 +425,13 @@
     <t>TC_APP_023 - Verify profile image upload simulation</t>
   </si>
   <si>
-    <t>5:33:19 PM</t>
-  </si>
-  <si>
-    <t>5:33:25 PM</t>
-  </si>
-  <si>
-    <t>3.35s</t>
+    <t>5:43:56 PM</t>
+  </si>
+  <si>
+    <t>5:44:02 PM</t>
+  </si>
+  <si>
+    <t>4.15s</t>
   </si>
   <si>
     <t>TC_APP_024</t>
@@ -446,13 +440,13 @@
     <t>TC_APP_024 - Verify change password form validation checks</t>
   </si>
   <si>
-    <t>5:33:31 PM</t>
-  </si>
-  <si>
-    <t>5:33:37 PM</t>
-  </si>
-  <si>
-    <t>3.18s</t>
+    <t>5:44:08 PM</t>
+  </si>
+  <si>
+    <t>5:44:14 PM</t>
+  </si>
+  <si>
+    <t>4.21s</t>
   </si>
   <si>
     <t>TC_APP_025</t>
@@ -461,13 +455,13 @@
     <t>TC_APP_025 - Verify successful change password submission</t>
   </si>
   <si>
-    <t>5:33:43 PM</t>
-  </si>
-  <si>
-    <t>5:33:49 PM</t>
-  </si>
-  <si>
-    <t>3.17s</t>
+    <t>5:44:20 PM</t>
+  </si>
+  <si>
+    <t>5:44:26 PM</t>
+  </si>
+  <si>
+    <t>2.18s</t>
   </si>
   <si>
     <t>TC_APP_026</t>
@@ -476,13 +470,13 @@
     <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
   </si>
   <si>
-    <t>5:33:55 PM</t>
-  </si>
-  <si>
-    <t>5:34:01 PM</t>
-  </si>
-  <si>
-    <t>3.37s</t>
+    <t>5:44:32 PM</t>
+  </si>
+  <si>
+    <t>5:44:38 PM</t>
+  </si>
+  <si>
+    <t>4.76s</t>
   </si>
   <si>
     <t>TC_APP_027</t>
@@ -491,13 +485,13 @@
     <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
   </si>
   <si>
-    <t>5:34:07 PM</t>
-  </si>
-  <si>
-    <t>5:34:13 PM</t>
-  </si>
-  <si>
-    <t>2.66s</t>
+    <t>5:44:44 PM</t>
+  </si>
+  <si>
+    <t>5:44:50 PM</t>
+  </si>
+  <si>
+    <t>2.73s</t>
   </si>
   <si>
     <t>TC_APP_028</t>
@@ -506,13 +500,13 @@
     <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
   </si>
   <si>
-    <t>5:34:19 PM</t>
-  </si>
-  <si>
-    <t>5:34:25 PM</t>
-  </si>
-  <si>
-    <t>3.81s</t>
+    <t>5:44:56 PM</t>
+  </si>
+  <si>
+    <t>5:45:02 PM</t>
+  </si>
+  <si>
+    <t>3.05s</t>
   </si>
   <si>
     <t>TC_APP_029</t>
@@ -521,10 +515,13 @@
     <t>TC_APP_029 - Verify logout button click asks confirmation</t>
   </si>
   <si>
-    <t>5:34:31 PM</t>
-  </si>
-  <si>
-    <t>5:34:37 PM</t>
+    <t>5:45:08 PM</t>
+  </si>
+  <si>
+    <t>5:45:14 PM</t>
+  </si>
+  <si>
+    <t>3.80s</t>
   </si>
   <si>
     <t>TC_APP_030</t>
@@ -533,13 +530,13 @@
     <t>TC_APP_030 - Verify successful logout clears local cache database</t>
   </si>
   <si>
-    <t>5:34:43 PM</t>
-  </si>
-  <si>
-    <t>5:34:49 PM</t>
-  </si>
-  <si>
-    <t>3.98s</t>
+    <t>5:45:20 PM</t>
+  </si>
+  <si>
+    <t>5:45:26 PM</t>
+  </si>
+  <si>
+    <t>2.21s</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -566,7 +563,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T12:04:55.279Z</t>
+    <t>2026-06-15T12:15:32.242Z</t>
   </si>
   <si>
     <t>Execution of TC_APP_001</t>
@@ -1605,423 +1602,423 @@
         <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="G24" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="G25" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="G29" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="G30" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2045,13 +2042,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>17</v>
@@ -2060,7 +2057,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2083,529 +2080,529 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2627,70 +2624,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:45:32 PM</t>
+    <t>6/15/2026, 6:07:07 PM</t>
   </si>
   <si>
     <t>Android Emulator (Pixel 6)</t>
@@ -92,13 +92,13 @@
     <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
   </si>
   <si>
-    <t>5:39:32 PM</t>
-  </si>
-  <si>
-    <t>5:39:38 PM</t>
-  </si>
-  <si>
-    <t>4.10s</t>
+    <t>6:01:07 PM</t>
+  </si>
+  <si>
+    <t>6:01:13 PM</t>
+  </si>
+  <si>
+    <t>3.93s</t>
   </si>
   <si>
     <t>TC_APP_002</t>
@@ -107,13 +107,13 @@
     <t>TC_APP_002 - Verify splash screen transition duration</t>
   </si>
   <si>
-    <t>5:39:44 PM</t>
-  </si>
-  <si>
-    <t>5:39:50 PM</t>
-  </si>
-  <si>
-    <t>2.80s</t>
+    <t>6:01:19 PM</t>
+  </si>
+  <si>
+    <t>6:01:25 PM</t>
+  </si>
+  <si>
+    <t>2.89s</t>
   </si>
   <si>
     <t>TC_APP_003</t>
@@ -122,13 +122,13 @@
     <t>TC_APP_003 - Verify registration page display inside app</t>
   </si>
   <si>
-    <t>5:39:56 PM</t>
-  </si>
-  <si>
-    <t>5:40:02 PM</t>
-  </si>
-  <si>
-    <t>4.37s</t>
+    <t>6:01:31 PM</t>
+  </si>
+  <si>
+    <t>6:01:37 PM</t>
+  </si>
+  <si>
+    <t>3.05s</t>
   </si>
   <si>
     <t>TC_APP_004</t>
@@ -137,13 +137,13 @@
     <t>TC_APP_004 - Verify new account registration via mobile form</t>
   </si>
   <si>
-    <t>5:40:08 PM</t>
-  </si>
-  <si>
-    <t>5:40:14 PM</t>
-  </si>
-  <si>
-    <t>4.53s</t>
+    <t>6:01:43 PM</t>
+  </si>
+  <si>
+    <t>6:01:49 PM</t>
+  </si>
+  <si>
+    <t>3.91s</t>
   </si>
   <si>
     <t>TC_APP_005</t>
@@ -152,13 +152,13 @@
     <t>TC_APP_005 - Verify app displays validation errors on registration</t>
   </si>
   <si>
-    <t>5:40:20 PM</t>
-  </si>
-  <si>
-    <t>5:40:26 PM</t>
-  </si>
-  <si>
-    <t>3.11s</t>
+    <t>6:01:55 PM</t>
+  </si>
+  <si>
+    <t>6:02:01 PM</t>
+  </si>
+  <si>
+    <t>2.57s</t>
   </si>
   <si>
     <t>TC_APP_006</t>
@@ -167,13 +167,13 @@
     <t>TC_APP_006 - Verify Login screen load and fields check</t>
   </si>
   <si>
-    <t>5:40:32 PM</t>
-  </si>
-  <si>
-    <t>5:40:38 PM</t>
-  </si>
-  <si>
-    <t>2.89s</t>
+    <t>6:02:07 PM</t>
+  </si>
+  <si>
+    <t>6:02:13 PM</t>
+  </si>
+  <si>
+    <t>4.97s</t>
   </si>
   <si>
     <t>TC_APP_007</t>
@@ -182,13 +182,13 @@
     <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
   </si>
   <si>
-    <t>5:40:44 PM</t>
-  </si>
-  <si>
-    <t>5:40:50 PM</t>
-  </si>
-  <si>
-    <t>2.85s</t>
+    <t>6:02:19 PM</t>
+  </si>
+  <si>
+    <t>6:02:25 PM</t>
+  </si>
+  <si>
+    <t>3.60s</t>
   </si>
   <si>
     <t>TC_APP_008</t>
@@ -197,13 +197,13 @@
     <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
   </si>
   <si>
-    <t>5:40:56 PM</t>
-  </si>
-  <si>
-    <t>5:41:02 PM</t>
-  </si>
-  <si>
-    <t>3.95s</t>
+    <t>6:02:31 PM</t>
+  </si>
+  <si>
+    <t>6:02:37 PM</t>
+  </si>
+  <si>
+    <t>4.83s</t>
   </si>
   <si>
     <t>TC_APP_009</t>
@@ -215,178 +215,181 @@
     <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
   </si>
   <si>
-    <t>5:41:08 PM</t>
-  </si>
-  <si>
-    <t>5:41:14 PM</t>
+    <t>6:02:43 PM</t>
+  </si>
+  <si>
+    <t>6:02:49 PM</t>
+  </si>
+  <si>
+    <t>2.35s</t>
+  </si>
+  <si>
+    <t>TC_APP_010</t>
+  </si>
+  <si>
+    <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
+  </si>
+  <si>
+    <t>6:02:55 PM</t>
+  </si>
+  <si>
+    <t>6:03:01 PM</t>
+  </si>
+  <si>
+    <t>2.44s</t>
+  </si>
+  <si>
+    <t>TC_APP_011</t>
+  </si>
+  <si>
+    <t>TC_APP_011 - Verify add income input dialog form</t>
+  </si>
+  <si>
+    <t>6:03:07 PM</t>
+  </si>
+  <si>
+    <t>6:03:13 PM</t>
+  </si>
+  <si>
+    <t>2.19s</t>
+  </si>
+  <si>
+    <t>TC_APP_012</t>
+  </si>
+  <si>
+    <t>TC_APP_012 - Verify add income form submission and balance update</t>
+  </si>
+  <si>
+    <t>6:03:19 PM</t>
+  </si>
+  <si>
+    <t>6:03:25 PM</t>
+  </si>
+  <si>
+    <t>2.42s</t>
+  </si>
+  <si>
+    <t>TC_APP_013</t>
+  </si>
+  <si>
+    <t>TC_APP_013 - Verify add expense input dialog form</t>
+  </si>
+  <si>
+    <t>6:03:31 PM</t>
+  </si>
+  <si>
+    <t>6:03:37 PM</t>
+  </si>
+  <si>
+    <t>2.22s</t>
+  </si>
+  <si>
+    <t>TC_APP_014</t>
+  </si>
+  <si>
+    <t>TC_APP_014 - Verify add expense form submission and balance update</t>
+  </si>
+  <si>
+    <t>6:03:43 PM</t>
+  </si>
+  <si>
+    <t>6:03:49 PM</t>
+  </si>
+  <si>
+    <t>4.59s</t>
+  </si>
+  <si>
+    <t>TC_APP_015</t>
+  </si>
+  <si>
+    <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
+  </si>
+  <si>
+    <t>6:03:55 PM</t>
+  </si>
+  <si>
+    <t>6:04:01 PM</t>
+  </si>
+  <si>
+    <t>4.70s</t>
+  </si>
+  <si>
+    <t>TC_APP_016</t>
+  </si>
+  <si>
+    <t>TC_APP_016 - Verify transaction title update and save action</t>
+  </si>
+  <si>
+    <t>6:04:07 PM</t>
+  </si>
+  <si>
+    <t>6:04:13 PM</t>
+  </si>
+  <si>
+    <t>2.33s</t>
+  </si>
+  <si>
+    <t>TC_APP_017</t>
+  </si>
+  <si>
+    <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
+  </si>
+  <si>
+    <t>6:04:19 PM</t>
+  </si>
+  <si>
+    <t>6:04:25 PM</t>
+  </si>
+  <si>
+    <t>4.40s</t>
+  </si>
+  <si>
+    <t>TC_APP_018</t>
+  </si>
+  <si>
+    <t>TC_APP_018 - Verify search transaction input box filters list</t>
+  </si>
+  <si>
+    <t>6:04:31 PM</t>
+  </si>
+  <si>
+    <t>6:04:37 PM</t>
+  </si>
+  <si>
+    <t>2.41s</t>
+  </si>
+  <si>
+    <t>TC_APP_019</t>
+  </si>
+  <si>
+    <t>Alerts OS</t>
+  </si>
+  <si>
+    <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
+  </si>
+  <si>
+    <t>6:04:43 PM</t>
+  </si>
+  <si>
+    <t>6:04:49 PM</t>
   </si>
   <si>
     <t>4.56s</t>
   </si>
   <si>
-    <t>TC_APP_010</t>
-  </si>
-  <si>
-    <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
-  </si>
-  <si>
-    <t>5:41:20 PM</t>
-  </si>
-  <si>
-    <t>5:41:26 PM</t>
-  </si>
-  <si>
-    <t>4.05s</t>
-  </si>
-  <si>
-    <t>TC_APP_011</t>
-  </si>
-  <si>
-    <t>TC_APP_011 - Verify add income input dialog form</t>
-  </si>
-  <si>
-    <t>5:41:32 PM</t>
-  </si>
-  <si>
-    <t>5:41:38 PM</t>
-  </si>
-  <si>
-    <t>3.42s</t>
-  </si>
-  <si>
-    <t>TC_APP_012</t>
-  </si>
-  <si>
-    <t>TC_APP_012 - Verify add income form submission and balance update</t>
-  </si>
-  <si>
-    <t>5:41:44 PM</t>
-  </si>
-  <si>
-    <t>5:41:50 PM</t>
-  </si>
-  <si>
-    <t>4.72s</t>
-  </si>
-  <si>
-    <t>TC_APP_013</t>
-  </si>
-  <si>
-    <t>TC_APP_013 - Verify add expense input dialog form</t>
-  </si>
-  <si>
-    <t>5:41:56 PM</t>
-  </si>
-  <si>
-    <t>5:42:02 PM</t>
-  </si>
-  <si>
-    <t>3.36s</t>
-  </si>
-  <si>
-    <t>TC_APP_014</t>
-  </si>
-  <si>
-    <t>TC_APP_014 - Verify add expense form submission and balance update</t>
-  </si>
-  <si>
-    <t>5:42:08 PM</t>
-  </si>
-  <si>
-    <t>5:42:14 PM</t>
-  </si>
-  <si>
-    <t>TC_APP_015</t>
-  </si>
-  <si>
-    <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
-  </si>
-  <si>
-    <t>5:42:20 PM</t>
-  </si>
-  <si>
-    <t>5:42:26 PM</t>
-  </si>
-  <si>
-    <t>4.79s</t>
-  </si>
-  <si>
-    <t>TC_APP_016</t>
-  </si>
-  <si>
-    <t>TC_APP_016 - Verify transaction title update and save action</t>
-  </si>
-  <si>
-    <t>5:42:32 PM</t>
-  </si>
-  <si>
-    <t>5:42:38 PM</t>
-  </si>
-  <si>
-    <t>4.43s</t>
-  </si>
-  <si>
-    <t>TC_APP_017</t>
-  </si>
-  <si>
-    <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
-  </si>
-  <si>
-    <t>5:42:44 PM</t>
-  </si>
-  <si>
-    <t>5:42:50 PM</t>
-  </si>
-  <si>
-    <t>2.31s</t>
-  </si>
-  <si>
-    <t>TC_APP_018</t>
-  </si>
-  <si>
-    <t>TC_APP_018 - Verify search transaction input box filters list</t>
-  </si>
-  <si>
-    <t>5:42:56 PM</t>
-  </si>
-  <si>
-    <t>5:43:02 PM</t>
-  </si>
-  <si>
-    <t>4.98s</t>
-  </si>
-  <si>
-    <t>TC_APP_019</t>
-  </si>
-  <si>
-    <t>Alerts OS</t>
-  </si>
-  <si>
-    <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
-  </si>
-  <si>
-    <t>5:43:08 PM</t>
-  </si>
-  <si>
-    <t>5:43:14 PM</t>
-  </si>
-  <si>
-    <t>2.53s</t>
-  </si>
-  <si>
     <t>TC_APP_020</t>
   </si>
   <si>
     <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
   </si>
   <si>
-    <t>5:43:20 PM</t>
-  </si>
-  <si>
-    <t>5:43:26 PM</t>
-  </si>
-  <si>
-    <t>2.04s</t>
+    <t>6:04:55 PM</t>
+  </si>
+  <si>
+    <t>6:05:01 PM</t>
+  </si>
+  <si>
+    <t>4.12s</t>
   </si>
   <si>
     <t>TC_APP_021</t>
@@ -395,10 +398,13 @@
     <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
   </si>
   <si>
-    <t>5:43:32 PM</t>
-  </si>
-  <si>
-    <t>5:43:38 PM</t>
+    <t>6:05:07 PM</t>
+  </si>
+  <si>
+    <t>6:05:13 PM</t>
+  </si>
+  <si>
+    <t>3.04s</t>
   </si>
   <si>
     <t>TC_APP_022</t>
@@ -410,13 +416,13 @@
     <t>TC_APP_022 - Verify profile update form saves new username</t>
   </si>
   <si>
-    <t>5:43:44 PM</t>
-  </si>
-  <si>
-    <t>5:43:50 PM</t>
-  </si>
-  <si>
-    <t>2.02s</t>
+    <t>6:05:19 PM</t>
+  </si>
+  <si>
+    <t>6:05:25 PM</t>
+  </si>
+  <si>
+    <t>4.78s</t>
   </si>
   <si>
     <t>TC_APP_023</t>
@@ -425,13 +431,13 @@
     <t>TC_APP_023 - Verify profile image upload simulation</t>
   </si>
   <si>
-    <t>5:43:56 PM</t>
-  </si>
-  <si>
-    <t>5:44:02 PM</t>
-  </si>
-  <si>
-    <t>4.15s</t>
+    <t>6:05:31 PM</t>
+  </si>
+  <si>
+    <t>6:05:37 PM</t>
+  </si>
+  <si>
+    <t>3.86s</t>
   </si>
   <si>
     <t>TC_APP_024</t>
@@ -440,13 +446,13 @@
     <t>TC_APP_024 - Verify change password form validation checks</t>
   </si>
   <si>
-    <t>5:44:08 PM</t>
-  </si>
-  <si>
-    <t>5:44:14 PM</t>
-  </si>
-  <si>
-    <t>4.21s</t>
+    <t>6:05:43 PM</t>
+  </si>
+  <si>
+    <t>6:05:49 PM</t>
+  </si>
+  <si>
+    <t>2.27s</t>
   </si>
   <si>
     <t>TC_APP_025</t>
@@ -455,13 +461,13 @@
     <t>TC_APP_025 - Verify successful change password submission</t>
   </si>
   <si>
-    <t>5:44:20 PM</t>
-  </si>
-  <si>
-    <t>5:44:26 PM</t>
-  </si>
-  <si>
-    <t>2.18s</t>
+    <t>6:05:55 PM</t>
+  </si>
+  <si>
+    <t>6:06:01 PM</t>
+  </si>
+  <si>
+    <t>2.34s</t>
   </si>
   <si>
     <t>TC_APP_026</t>
@@ -470,13 +476,13 @@
     <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
   </si>
   <si>
-    <t>5:44:32 PM</t>
-  </si>
-  <si>
-    <t>5:44:38 PM</t>
-  </si>
-  <si>
-    <t>4.76s</t>
+    <t>6:06:07 PM</t>
+  </si>
+  <si>
+    <t>6:06:13 PM</t>
+  </si>
+  <si>
+    <t>3.75s</t>
   </si>
   <si>
     <t>TC_APP_027</t>
@@ -485,13 +491,13 @@
     <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
   </si>
   <si>
-    <t>5:44:44 PM</t>
-  </si>
-  <si>
-    <t>5:44:50 PM</t>
-  </si>
-  <si>
-    <t>2.73s</t>
+    <t>6:06:19 PM</t>
+  </si>
+  <si>
+    <t>6:06:25 PM</t>
+  </si>
+  <si>
+    <t>2.03s</t>
   </si>
   <si>
     <t>TC_APP_028</t>
@@ -500,13 +506,13 @@
     <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
   </si>
   <si>
-    <t>5:44:56 PM</t>
-  </si>
-  <si>
-    <t>5:45:02 PM</t>
-  </si>
-  <si>
-    <t>3.05s</t>
+    <t>6:06:31 PM</t>
+  </si>
+  <si>
+    <t>6:06:37 PM</t>
+  </si>
+  <si>
+    <t>4.58s</t>
   </si>
   <si>
     <t>TC_APP_029</t>
@@ -515,13 +521,10 @@
     <t>TC_APP_029 - Verify logout button click asks confirmation</t>
   </si>
   <si>
-    <t>5:45:08 PM</t>
-  </si>
-  <si>
-    <t>5:45:14 PM</t>
-  </si>
-  <si>
-    <t>3.80s</t>
+    <t>6:06:43 PM</t>
+  </si>
+  <si>
+    <t>6:06:49 PM</t>
   </si>
   <si>
     <t>TC_APP_030</t>
@@ -530,13 +533,10 @@
     <t>TC_APP_030 - Verify successful logout clears local cache database</t>
   </si>
   <si>
-    <t>5:45:20 PM</t>
-  </si>
-  <si>
-    <t>5:45:26 PM</t>
-  </si>
-  <si>
-    <t>2.21s</t>
+    <t>6:06:55 PM</t>
+  </si>
+  <si>
+    <t>6:07:01 PM</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -563,7 +563,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T12:15:32.242Z</t>
+    <t>2026-06-15T12:37:07.310Z</t>
   </si>
   <si>
     <t>Execution of TC_APP_001</t>
@@ -1602,18 +1602,18 @@
         <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1622,24 +1622,24 @@
         <v>4</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1648,24 +1648,24 @@
         <v>4</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1674,24 +1674,24 @@
         <v>4</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1700,24 +1700,24 @@
         <v>4</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1726,24 +1726,24 @@
         <v>4</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1752,24 +1752,24 @@
         <v>4</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1778,24 +1778,24 @@
         <v>4</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1804,24 +1804,24 @@
         <v>4</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1830,24 +1830,24 @@
         <v>4</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1856,24 +1856,24 @@
         <v>4</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1882,24 +1882,24 @@
         <v>4</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -1908,24 +1908,24 @@
         <v>4</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -1934,24 +1934,24 @@
         <v>4</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
@@ -1960,24 +1960,24 @@
         <v>4</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -1986,24 +1986,24 @@
         <v>4</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -2012,13 +2012,13 @@
         <v>4</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>173</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2338,7 +2338,7 @@
         <v>182</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>199</v>
@@ -2355,7 +2355,7 @@
         <v>182</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>200</v>
@@ -2372,7 +2372,7 @@
         <v>182</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>201</v>
@@ -2389,7 +2389,7 @@
         <v>182</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>202</v>
@@ -2406,7 +2406,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>203</v>
@@ -2423,7 +2423,7 @@
         <v>182</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>204</v>
@@ -2440,7 +2440,7 @@
         <v>182</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>205</v>
@@ -2457,7 +2457,7 @@
         <v>182</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>206</v>
@@ -2474,7 +2474,7 @@
         <v>182</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>207</v>
@@ -2491,7 +2491,7 @@
         <v>182</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>208</v>
@@ -2508,7 +2508,7 @@
         <v>182</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>209</v>
@@ -2525,7 +2525,7 @@
         <v>182</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>210</v>
@@ -2542,7 +2542,7 @@
         <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>211</v>
@@ -2559,7 +2559,7 @@
         <v>182</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>212</v>
@@ -2576,7 +2576,7 @@
         <v>182</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>213</v>
@@ -2593,7 +2593,7 @@
         <v>182</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>214</v>
